--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20261015.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20261015.xlsx
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>153,499</t>
+          <t>546,404</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>546,404</t>
+          <t>153,499</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>580,000</t>
+          <t>811,897</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>811,897</t>
+          <t>580,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,839,000</t>
+          <t>6,337,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>6,337,000</t>
+          <t>1,839,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>3,492,981</t>
+          <t>3,318,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>3,318,000</t>
+          <t>3,492,981</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>940,659</t>
+          <t>1,201,441</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>1,201,441</t>
+          <t>940,659</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>1,315,384</t>
+          <t>584,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>584,000</t>
+          <t>1,315,384</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>779,000</t>
+          <t>1,189,076</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>1,189,076</t>
+          <t>779,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>291,000</t>
+          <t>321,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>321,000</t>
+          <t>291,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>1,722,640</t>
+          <t>182,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>182,000</t>
+          <t>1,722,640</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>晶豪科</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>171,000</t>
+          <t>416,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>64,538</t>
+          <t>171,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>晶豪科</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>416,000</t>
+          <t>64,538</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>157,000</t>
+          <t>682,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>682,000</t>
+          <t>157,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
